--- a/inputData/LTM_demandBFinal.xlsx
+++ b/inputData/LTM_demandBFinal.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,19 +465,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -488,16 +488,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -505,19 +505,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -525,13 +525,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -545,19 +545,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -565,19 +565,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -585,13 +585,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="E8" t="n">
         <v>4</v>
@@ -605,13 +605,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="E9" t="n">
         <v>4</v>
@@ -625,16 +625,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -645,19 +645,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -665,16 +665,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -685,19 +685,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -705,19 +705,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="E14" t="n">
         <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -725,16 +725,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -745,16 +745,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -768,13 +768,13 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -791,10 +791,10 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -811,7 +811,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="E19" t="n">
         <v>2</v>
@@ -825,19 +825,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -845,19 +845,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -865,16 +865,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -885,16 +885,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -908,16 +908,16 @@
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -925,19 +925,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -945,19 +945,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>148</v>
+        <v>187</v>
       </c>
       <c r="E26" t="n">
         <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -965,16 +965,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D27" t="n">
-        <v>148</v>
+        <v>198</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -988,13 +988,13 @@
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>153</v>
+        <v>231</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
@@ -1008,16 +1008,16 @@
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>163</v>
+        <v>249</v>
       </c>
       <c r="E29" t="n">
         <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1025,16 +1025,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>167</v>
+        <v>278</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1051,10 +1051,10 @@
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>175</v>
+        <v>407</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1068,16 +1068,16 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>181</v>
+        <v>423</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1085,19 +1085,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D33" t="n">
-        <v>184</v>
+        <v>426</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1105,13 +1105,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>190</v>
+        <v>450</v>
       </c>
       <c r="E34" t="n">
         <v>4</v>
@@ -1125,19 +1125,19 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>190</v>
+        <v>452</v>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1145,16 +1145,16 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D36" t="n">
-        <v>413</v>
+        <v>457</v>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -1165,19 +1165,19 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D37" t="n">
-        <v>464</v>
+        <v>490</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1185,19 +1185,19 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>471</v>
+        <v>514</v>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1205,19 +1205,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1225,16 +1225,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -1245,19 +1245,19 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1265,19 +1265,19 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D42" t="n">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1285,19 +1285,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1305,19 +1305,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1328,16 +1328,16 @@
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D45" t="n">
-        <v>575</v>
+        <v>558</v>
       </c>
       <c r="E45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -1345,16 +1345,16 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D46" t="n">
-        <v>581</v>
+        <v>561</v>
       </c>
       <c r="E46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
@@ -1365,13 +1365,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>587</v>
+        <v>561</v>
       </c>
       <c r="E47" t="n">
         <v>3</v>
@@ -1391,10 +1391,10 @@
         <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>610</v>
+        <v>564</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F48" t="n">
         <v>1</v>
@@ -1405,19 +1405,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>660</v>
+        <v>564</v>
       </c>
       <c r="E49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1425,19 +1425,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>663</v>
+        <v>571</v>
       </c>
       <c r="E50" t="n">
         <v>3</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1445,19 +1445,19 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>664</v>
+        <v>582</v>
       </c>
       <c r="E51" t="n">
         <v>4</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -1468,16 +1468,16 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D52" t="n">
-        <v>667</v>
+        <v>587</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1485,16 +1485,16 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D53" t="n">
-        <v>667</v>
+        <v>589</v>
       </c>
       <c r="E53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
@@ -1505,13 +1505,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D54" t="n">
-        <v>671</v>
+        <v>605</v>
       </c>
       <c r="E54" t="n">
         <v>4</v>
@@ -1525,16 +1525,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D55" t="n">
-        <v>672</v>
+        <v>608</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -1545,16 +1545,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>693</v>
+        <v>616</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>1</v>
@@ -1565,16 +1565,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D57" t="n">
-        <v>694</v>
+        <v>617</v>
       </c>
       <c r="E57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -1585,18 +1585,158 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D58" t="n">
-        <v>760</v>
+        <v>651</v>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="n">
+        <v>7</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>661</v>
+      </c>
+      <c r="E59" t="n">
+        <v>4</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="n">
+        <v>7</v>
+      </c>
+      <c r="D60" t="n">
+        <v>666</v>
+      </c>
+      <c r="E60" t="n">
+        <v>3</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" t="n">
+        <v>695</v>
+      </c>
+      <c r="E61" t="n">
+        <v>3</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="n">
+        <v>7</v>
+      </c>
+      <c r="C62" t="n">
+        <v>5</v>
+      </c>
+      <c r="D62" t="n">
+        <v>696</v>
+      </c>
+      <c r="E62" t="n">
+        <v>3</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="n">
+        <v>9</v>
+      </c>
+      <c r="D63" t="n">
+        <v>696</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="n">
+        <v>6</v>
+      </c>
+      <c r="C64" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" t="n">
+        <v>763</v>
+      </c>
+      <c r="E64" t="n">
+        <v>3</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="n">
+        <v>4</v>
+      </c>
+      <c r="D65" t="n">
+        <v>764</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" t="n">
         <v>1</v>
       </c>
     </row>

--- a/inputData/LTM_demandBFinal.xlsx
+++ b/inputData/LTM_demandBFinal.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,19 +465,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -485,19 +485,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E3" t="n">
         <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -505,16 +505,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -525,13 +525,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -545,19 +545,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="E6" t="n">
         <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -565,19 +565,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -605,16 +605,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -625,13 +625,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="E10" t="n">
         <v>4</v>
@@ -645,16 +645,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -665,19 +665,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -685,16 +685,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -711,13 +711,13 @@
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E14" t="n">
         <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -725,16 +725,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -745,19 +745,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -765,16 +765,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -785,13 +785,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E18" t="n">
         <v>4</v>
@@ -805,16 +805,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -825,16 +825,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -851,13 +851,13 @@
         <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -865,16 +865,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -885,19 +885,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -908,16 +908,16 @@
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="E24" t="n">
         <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -925,19 +925,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -948,16 +948,16 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -971,13 +971,13 @@
         <v>7</v>
       </c>
       <c r="D27" t="n">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="E27" t="n">
         <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -985,19 +985,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1005,13 +1005,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>249</v>
+        <v>418</v>
       </c>
       <c r="E29" t="n">
         <v>4</v>
@@ -1025,13 +1025,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>278</v>
+        <v>425</v>
       </c>
       <c r="E30" t="n">
         <v>4</v>
@@ -1048,13 +1048,13 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>407</v>
+        <v>433</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1068,16 +1068,16 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>423</v>
+        <v>476</v>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1085,16 +1085,16 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>426</v>
+        <v>486</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
         <v>1</v>
@@ -1105,16 +1105,16 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>450</v>
+        <v>492</v>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -1125,19 +1125,19 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D35" t="n">
-        <v>452</v>
+        <v>509</v>
       </c>
       <c r="E35" t="n">
         <v>4</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1145,19 +1145,19 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C36" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D36" t="n">
-        <v>457</v>
+        <v>520</v>
       </c>
       <c r="E36" t="n">
         <v>4</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1165,16 +1165,16 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D37" t="n">
-        <v>490</v>
+        <v>532</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37" t="n">
         <v>1</v>
@@ -1185,16 +1185,16 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D38" t="n">
-        <v>514</v>
+        <v>533</v>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
         <v>1</v>
@@ -1205,19 +1205,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1225,16 +1225,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>526</v>
+        <v>544</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -1245,19 +1245,19 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>529</v>
+        <v>545</v>
       </c>
       <c r="E41" t="n">
         <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1271,13 +1271,13 @@
         <v>7</v>
       </c>
       <c r="D42" t="n">
-        <v>543</v>
+        <v>559</v>
       </c>
       <c r="E42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1285,13 +1285,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D43" t="n">
-        <v>549</v>
+        <v>565</v>
       </c>
       <c r="E43" t="n">
         <v>4</v>
@@ -1305,13 +1305,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D44" t="n">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="E44" t="n">
         <v>4</v>
@@ -1328,16 +1328,16 @@
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D45" t="n">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1345,19 +1345,19 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C46" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>561</v>
+        <v>580</v>
       </c>
       <c r="E46" t="n">
         <v>3</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1365,19 +1365,19 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>561</v>
+        <v>587</v>
       </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -1385,13 +1385,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="E48" t="n">
         <v>4</v>
@@ -1405,19 +1405,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>564</v>
+        <v>591</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -1425,19 +1425,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D50" t="n">
-        <v>571</v>
+        <v>608</v>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -1445,16 +1445,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>582</v>
+        <v>609</v>
       </c>
       <c r="E51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
         <v>1</v>
@@ -1468,16 +1468,16 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D52" t="n">
-        <v>587</v>
+        <v>636</v>
       </c>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -1485,13 +1485,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C53" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D53" t="n">
-        <v>589</v>
+        <v>641</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
@@ -1505,16 +1505,16 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D54" t="n">
-        <v>605</v>
+        <v>666</v>
       </c>
       <c r="E54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -1525,16 +1525,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C55" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>608</v>
+        <v>691</v>
       </c>
       <c r="E55" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -1545,16 +1545,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D56" t="n">
-        <v>616</v>
+        <v>693</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
         <v>1</v>
@@ -1565,16 +1565,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C57" t="n">
         <v>6</v>
       </c>
       <c r="D57" t="n">
-        <v>617</v>
+        <v>695</v>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -1585,13 +1585,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C58" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>651</v>
+        <v>696</v>
       </c>
       <c r="E58" t="n">
         <v>3</v>
@@ -1605,19 +1605,19 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>661</v>
+        <v>714</v>
       </c>
       <c r="E59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1625,19 +1625,19 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C60" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>666</v>
+        <v>715</v>
       </c>
       <c r="E60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -1645,19 +1645,19 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>695</v>
+        <v>732</v>
       </c>
       <c r="E61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -1665,19 +1665,19 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D62" t="n">
-        <v>696</v>
+        <v>749</v>
       </c>
       <c r="E62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -1685,59 +1685,19 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C63" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
-        <v>696</v>
+        <v>757</v>
       </c>
       <c r="E63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" t="n">
-        <v>6</v>
-      </c>
-      <c r="C64" t="n">
-        <v>2</v>
-      </c>
-      <c r="D64" t="n">
-        <v>763</v>
-      </c>
-      <c r="E64" t="n">
-        <v>3</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" t="n">
-        <v>1</v>
-      </c>
-      <c r="C65" t="n">
-        <v>4</v>
-      </c>
-      <c r="D65" t="n">
-        <v>764</v>
-      </c>
-      <c r="E65" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/inputData/LTM_demandBFinal.xlsx
+++ b/inputData/LTM_demandBFinal.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,19 +465,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -485,19 +485,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E3" t="n">
         <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -508,16 +508,16 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -525,19 +525,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -545,19 +545,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -565,16 +565,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -588,16 +588,16 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -605,16 +605,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
         <v>2</v>
       </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
       <c r="D9" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -628,10 +628,10 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="E10" t="n">
         <v>4</v>
@@ -645,19 +645,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -665,19 +665,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -685,13 +685,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E13" t="n">
         <v>4</v>
@@ -705,19 +705,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E14" t="n">
         <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -725,13 +725,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
@@ -745,16 +745,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
@@ -765,16 +765,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -785,16 +785,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -805,19 +805,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -831,7 +831,7 @@
         <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="E20" t="n">
         <v>4</v>
@@ -848,13 +848,13 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -865,19 +865,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>173</v>
+        <v>146</v>
       </c>
       <c r="E22" t="n">
         <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -885,19 +885,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -905,16 +905,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -928,13 +928,13 @@
         <v>1</v>
       </c>
       <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>158</v>
+      </c>
+      <c r="E25" t="n">
         <v>2</v>
-      </c>
-      <c r="D25" t="n">
-        <v>182</v>
-      </c>
-      <c r="E25" t="n">
-        <v>4</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -945,13 +945,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="E26" t="n">
         <v>4</v>
@@ -965,19 +965,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>214</v>
+        <v>169</v>
       </c>
       <c r="E27" t="n">
         <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -985,16 +985,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>230</v>
+        <v>176</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1005,16 +1005,16 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>418</v>
+        <v>178</v>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -1025,16 +1025,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>425</v>
+        <v>186</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1045,16 +1045,16 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
         <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>433</v>
+        <v>186</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1068,10 +1068,10 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>476</v>
+        <v>188</v>
       </c>
       <c r="E32" t="n">
         <v>3</v>
@@ -1085,19 +1085,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D33" t="n">
-        <v>486</v>
+        <v>205</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1105,19 +1105,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>492</v>
+        <v>321</v>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1125,16 +1125,16 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>509</v>
+        <v>326</v>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
@@ -1148,13 +1148,13 @@
         <v>7</v>
       </c>
       <c r="C36" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>520</v>
+        <v>340</v>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
@@ -1165,16 +1165,16 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C37" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>532</v>
+        <v>344</v>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F37" t="n">
         <v>1</v>
@@ -1191,13 +1191,13 @@
         <v>7</v>
       </c>
       <c r="D38" t="n">
-        <v>533</v>
+        <v>377</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1205,19 +1205,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>541</v>
+        <v>388</v>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1225,16 +1225,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>544</v>
+        <v>409</v>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -1245,19 +1245,19 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>545</v>
+        <v>445</v>
       </c>
       <c r="E41" t="n">
         <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1268,13 +1268,13 @@
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D42" t="n">
-        <v>559</v>
+        <v>484</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
@@ -1285,16 +1285,16 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D43" t="n">
-        <v>565</v>
+        <v>484</v>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -1305,16 +1305,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C44" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>568</v>
+        <v>491</v>
       </c>
       <c r="E44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -1328,16 +1328,16 @@
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D45" t="n">
-        <v>570</v>
+        <v>514</v>
       </c>
       <c r="E45" t="n">
         <v>4</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -1345,19 +1345,19 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D46" t="n">
-        <v>580</v>
+        <v>550</v>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1365,19 +1365,19 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="E47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1391,7 +1391,7 @@
         <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="E48" t="n">
         <v>4</v>
@@ -1405,19 +1405,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1428,13 +1428,13 @@
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D50" t="n">
-        <v>608</v>
+        <v>585</v>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F50" t="n">
         <v>1</v>
@@ -1445,19 +1445,19 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D51" t="n">
-        <v>609</v>
+        <v>591</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1468,16 +1468,16 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D52" t="n">
-        <v>636</v>
+        <v>599</v>
       </c>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1485,19 +1485,19 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>641</v>
+        <v>616</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1505,16 +1505,16 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C54" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>666</v>
+        <v>641</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -1525,19 +1525,19 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D55" t="n">
-        <v>691</v>
+        <v>645</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -1545,19 +1545,19 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C56" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D56" t="n">
-        <v>693</v>
+        <v>658</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1565,16 +1565,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D57" t="n">
-        <v>695</v>
+        <v>674</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -1591,10 +1591,10 @@
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>696</v>
+        <v>676</v>
       </c>
       <c r="E58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F58" t="n">
         <v>1</v>
@@ -1605,13 +1605,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D59" t="n">
-        <v>714</v>
+        <v>677</v>
       </c>
       <c r="E59" t="n">
         <v>3</v>
@@ -1625,79 +1625,19 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D60" t="n">
-        <v>715</v>
+        <v>751</v>
       </c>
       <c r="E60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F60" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" t="n">
-        <v>7</v>
-      </c>
-      <c r="C61" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" t="n">
-        <v>732</v>
-      </c>
-      <c r="E61" t="n">
-        <v>2</v>
-      </c>
-      <c r="F61" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" t="n">
-        <v>1</v>
-      </c>
-      <c r="C62" t="n">
-        <v>4</v>
-      </c>
-      <c r="D62" t="n">
-        <v>749</v>
-      </c>
-      <c r="E62" t="n">
-        <v>2</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" t="n">
-        <v>8</v>
-      </c>
-      <c r="C63" t="n">
-        <v>4</v>
-      </c>
-      <c r="D63" t="n">
-        <v>757</v>
-      </c>
-      <c r="E63" t="n">
-        <v>3</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
